--- a/LubanConfig/MiniTemplate/Datas/__beans__.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/__beans__.xlsx
@@ -1,145 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52892A95-BBDD-42B6-A9C8-E869A5FA9CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>parent</t>
-  </si>
-  <si>
-    <t>valueType</t>
-  </si>
-  <si>
-    <t>sep</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*fields</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>分割符</t>
-  </si>
-  <si>
-    <t>字段名</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>分组</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>alias</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>字段别名</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>variants</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>字段变体</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="等线"/>
       <family val="2"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="等线"/>
       <family val="2"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -167,45 +84,105 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="差" xfId="2" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="差" xfId="2" builtinId="27"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -466,116 +443,344 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="6" width="12.25" customWidth="1"/>
-    <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col width="20.625" customWidth="1" style="4" min="2" max="4"/>
+    <col width="12.25" customWidth="1" style="4" min="5" max="6"/>
+    <col width="15" customWidth="1" style="4" min="7" max="9"/>
+    <col width="13.5" customWidth="1" style="4" min="10" max="12"/>
+    <col width="10.375" customWidth="1" style="4" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>22</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>valueType</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>sep</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>*fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>variants</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>分割符</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>字段名</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>字段别名</t>
+        </is>
+      </c>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="N3" s="0" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>字段变体</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>TaskData</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr"/>
+      <c r="D4" s="0" t="inlineStr"/>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>任务配置数据</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t>taskID</t>
+        </is>
+      </c>
+      <c r="L5" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N5" s="0" t="inlineStr">
+        <is>
+          <t>任务唯一ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>taskDesc</t>
+        </is>
+      </c>
+      <c r="L6" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N6" s="0" t="inlineStr">
+        <is>
+          <t>任务描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>taskType</t>
+        </is>
+      </c>
+      <c r="L7" s="0" t="inlineStr">
+        <is>
+          <t>TaskType</t>
+        </is>
+      </c>
+      <c r="N7" s="0" t="inlineStr">
+        <is>
+          <t>任务类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>targetCount</t>
+        </is>
+      </c>
+      <c r="L8" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N8" s="0" t="inlineStr">
+        <is>
+          <t>目标数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>isUnlock</t>
+        </is>
+      </c>
+      <c r="L9" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N9" s="0" t="inlineStr">
+        <is>
+          <t>是否默认解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>depotIds</t>
+        </is>
+      </c>
+      <c r="L10" s="0" t="inlineStr">
+        <is>
+          <t>list,int</t>
+        </is>
+      </c>
+      <c r="N10" s="0" t="inlineStr">
+        <is>
+          <t>驱动盘奖励id列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>materialsId</t>
+        </is>
+      </c>
+      <c r="L11" s="0" t="inlineStr">
+        <is>
+          <t>list,int</t>
+        </is>
+      </c>
+      <c r="N11" s="0" t="inlineStr">
+        <is>
+          <t>材料奖励id列表</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/LubanConfig/MiniTemplate/Datas/__beans__.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/__beans__.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="4" min="2" max="4"/>
@@ -776,6 +776,861 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MaterialData</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>材料配置数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>materialId</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>材料/物品编号（5-9，与驱动盘 1-4 同一编号表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>材料名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>iconName</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>图标资源名（对应 Resources/Res 下的名字）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>expValue</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>该材料提供的经验数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DriverDisk</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>驱动盘配置数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>depotId</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>驱动盘编号（1-4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>depotName</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>驱动盘名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>iconName</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>图标资源名（对应 Resources/Res 下的名字）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>initLevel</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>初始等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>initMaxFill</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>初始升级所需经验上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>upgradeMaterials</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>list,int</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>升级所需材料编号列表（逗号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>diskType</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>DriverDiskType</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>驱动盘类型（决定升级提升哪条属性）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>baseValue</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>基础数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>attackPercent</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>攻击加成%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>defensePercent</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>防御加成%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>healthPercent</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>生命加成%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>baoJiPercent</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>暴击加成%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Dialogue</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>一段剧情对话</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>对话编号</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>taskIds</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>list,int</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>对话结束后解锁的任务 id 列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>canSkip</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>是否允许 ESC 跳过</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>autoAdvance</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>是否自动前进</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>autoAdvanceDelay</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>自动前进延迟（秒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DialogueLine</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>对话中的一行</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>行编号（全局唯一）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>dialogueId</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>所属对话 id</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>lineIndex</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>在该对话中的顺序（从 0 开始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>speakerName</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>说话者名字（"玩家" 会显示在左侧）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>对话内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>portrait</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>立绘地址（Addressable 地址，未标记时回退 Resources.Load）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>voice</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>语音地址，留空则无</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>endAfterThis</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>本行显示后是否直接等待结束</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>DialogueOption</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>对话的选项分支</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>选项编号（全局唯一）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>lineId</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>所属对话行 id</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>optionIndex</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>在该行中的顺序（从 0 开始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>optionText</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>选项文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>nextLineIndex</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>选择后跳转到的行号，-1 表示结束对话</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>isTriggerEvent</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>结束对话时是否执行剧情收尾（解锁任务 / 生成敌人）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/LubanConfig/MiniTemplate/Datas/__beans__.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/__beans__.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="4" min="2" max="4"/>
@@ -782,14 +782,19 @@
           <t>##var</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MaterialData</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>材料配置数据</t>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>depotNums</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>list,int</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>驱动盘奖励数量列表（与 depotIds 一一对应，缺省按 1）</t>
         </is>
       </c>
     </row>
@@ -801,831 +806,870 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>materialNums</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>list,int</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>材料奖励数量列表（与 materialsId 一一对应，缺省按 1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>MaterialData</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>材料配置数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
           <t>materialId</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L15" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N15" s="0" t="inlineStr">
         <is>
           <t>材料/物品编号（5-9，与驱动盘 1-4 同一编号表）</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L16" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N16" s="0" t="inlineStr">
         <is>
           <t>材料名称</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>iconName</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L17" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N17" s="0" t="inlineStr">
         <is>
           <t>图标资源名（对应 Resources/Res 下的名字）</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>expValue</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L18" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N18" s="0" t="inlineStr">
         <is>
           <t>该材料提供的经验数值</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>DriverDisk</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>驱动盘配置数据</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>depotId</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L20" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N20" s="0" t="inlineStr">
         <is>
           <t>驱动盘编号（1-4）</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
         <is>
           <t>depotName</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L21" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N21" s="0" t="inlineStr">
         <is>
           <t>驱动盘名称</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t>iconName</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L22" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N22" s="0" t="inlineStr">
         <is>
           <t>图标资源名（对应 Resources/Res 下的名字）</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t>initLevel</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L23" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N23" s="0" t="inlineStr">
         <is>
           <t>初始等级</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t>initMaxFill</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L24" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N24" s="0" t="inlineStr">
         <is>
           <t>初始升级所需经验上限</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
         <is>
           <t>upgradeMaterials</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L25" s="0" t="inlineStr">
         <is>
           <t>list,int</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N25" s="0" t="inlineStr">
         <is>
           <t>升级所需材料编号列表（逗号分隔）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
         <is>
           <t>diskType</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L26" s="0" t="inlineStr">
         <is>
           <t>DriverDiskType</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N26" s="0" t="inlineStr">
         <is>
           <t>驱动盘类型（决定升级提升哪条属性）</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
         <is>
           <t>baseValue</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L27" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N27" s="0" t="inlineStr">
         <is>
           <t>基础数值</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t>attackPercent</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L28" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N28" s="0" t="inlineStr">
         <is>
           <t>攻击加成%</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
         <is>
           <t>defensePercent</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L29" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N29" s="0" t="inlineStr">
         <is>
           <t>防御加成%</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t>healthPercent</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L30" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N30" s="0" t="inlineStr">
         <is>
           <t>生命加成%</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="inlineStr">
         <is>
           <t>baoJiPercent</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L31" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N31" s="0" t="inlineStr">
         <is>
           <t>暴击加成%</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>Dialogue</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>一段剧情对话</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L33" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N33" s="0" t="inlineStr">
         <is>
           <t>对话编号</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="inlineStr">
         <is>
           <t>taskIds</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L34" s="0" t="inlineStr">
         <is>
           <t>list,int</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N34" s="0" t="inlineStr">
         <is>
           <t>对话结束后解锁的任务 id 列表</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="inlineStr">
         <is>
           <t>canSkip</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L35" s="0" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N35" s="0" t="inlineStr">
         <is>
           <t>是否允许 ESC 跳过</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="inlineStr">
         <is>
           <t>autoAdvance</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L36" s="0" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N36" s="0" t="inlineStr">
         <is>
           <t>是否自动前进</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="inlineStr">
         <is>
           <t>autoAdvanceDelay</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L37" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N37" s="0" t="inlineStr">
         <is>
           <t>自动前进延迟（秒）</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>DialogueLine</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>对话中的一行</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L39" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N39" s="0" t="inlineStr">
         <is>
           <t>行编号（全局唯一）</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J40" s="0" t="inlineStr">
         <is>
           <t>dialogueId</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L40" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N40" s="0" t="inlineStr">
         <is>
           <t>所属对话 id</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="inlineStr">
         <is>
           <t>lineIndex</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L41" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N41" s="0" t="inlineStr">
         <is>
           <t>在该对话中的顺序（从 0 开始）</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
         <is>
           <t>speakerName</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L42" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N42" s="0" t="inlineStr">
         <is>
           <t>说话者名字（"玩家" 会显示在左侧）</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J43" s="0" t="inlineStr">
         <is>
           <t>content</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L43" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N43" s="0" t="inlineStr">
         <is>
           <t>对话内容</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="inlineStr">
         <is>
           <t>portrait</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L44" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N44" s="0" t="inlineStr">
         <is>
           <t>立绘地址（Addressable 地址，未标记时回退 Resources.Load）</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="inlineStr">
         <is>
           <t>voice</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L45" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N45" s="0" t="inlineStr">
         <is>
           <t>语音地址，留空则无</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="inlineStr">
         <is>
           <t>endAfterThis</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L46" s="0" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N46" s="0" t="inlineStr">
         <is>
           <t>本行显示后是否直接等待结束</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>DialogueOption</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G47" s="0" t="inlineStr">
         <is>
           <t>对话的选项分支</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L48" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N48" s="0" t="inlineStr">
         <is>
           <t>选项编号（全局唯一）</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J49" s="0" t="inlineStr">
         <is>
           <t>lineId</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L49" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N49" s="0" t="inlineStr">
         <is>
           <t>所属对话行 id</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="inlineStr">
         <is>
           <t>optionIndex</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L50" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="N50" s="0" t="inlineStr">
         <is>
           <t>在该行中的顺序（从 0 开始）</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J51" s="0" t="inlineStr">
         <is>
           <t>optionText</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L51" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N51" s="0" t="inlineStr">
         <is>
           <t>选项文本</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J52" s="0" t="inlineStr">
         <is>
           <t>nextLineIndex</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L52" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N52" s="0" t="inlineStr">
         <is>
           <t>选择后跳转到的行号，-1 表示结束对话</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="J53" s="0" t="inlineStr">
         <is>
           <t>isTriggerEvent</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L53" s="0" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N53" s="0" t="inlineStr">
         <is>
           <t>结束对话时是否执行剧情收尾（解锁任务 / 生成敌人）</t>
         </is>
